--- a/data/templates/PANEL_0_PROTAGONISTAS.xlsx
+++ b/data/templates/PANEL_0_PROTAGONISTAS.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROTAGONISTAS_READINESS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAPACIDADES_POR_ACTOR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BARRERAS_POR_ACTOR" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,26 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00667eea"/>
-        <bgColor rgb="00667eea"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -54,25 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,324 +415,113 @@
   </sheetPr>
   <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Actor</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Readiness_Actual</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Readiness_Requerido</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Brecha</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Historial_12m</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Cambio_12m</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Tendencia</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Volatilidad</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Alertas</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Descripcion_Alerta</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Comunidad Local</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="D2" s="2">
-        <f>B2-C2</f>
-        <v/>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2">
-        <f>B2-E2</f>
-        <v/>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Diálogos iniciados</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno Local</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="D3" s="2">
-        <f>B3-C3</f>
-        <v/>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2">
-        <f>B3-E3</f>
-        <v/>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Cambio político</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Proveedores Técnicos</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="D4" s="2">
-        <f>B4-C4</f>
-        <v/>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="F4" s="2">
-        <f>B4-E4</f>
-        <v/>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Actores Económicos</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="D5" s="2">
-        <f>B5-C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="F5" s="2">
-        <f>B5-E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Actores Externos</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="D6" s="2">
-        <f>B6-C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="F6" s="2">
-        <f>B6-E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Fondos restringidos</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Estructura pendiente de llenar</t>
+          <t>Actor</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Readiness_Actual</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Readiness_Requerido</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Brecha</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Historial_12m</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Cambio_12m</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Tendencia</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volatilidad</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Alertas</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Descripcion_Alerta</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Estructura pendiente de llenar</t>
-        </is>
-      </c>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Comunidad Local</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gobierno Local</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Proveedores Técnicos</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Actores Económicos</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Actores Externos</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
